--- a/data/trans_orig/IMC_inf_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>29888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>48500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52479</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74996</t>
+          <t>74929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>68671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85167</t>
+          <t>85484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56325</t>
+          <t>56858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75180</t>
+          <t>75507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128131</t>
+          <t>129861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154591</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>22076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>44719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44748</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62488</t>
+          <t>61768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76248</t>
+          <t>74865</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100928</t>
+          <t>99423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92366</t>
+          <t>92068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111934</t>
+          <t>111759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98934</t>
+          <t>99341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176015</t>
+          <t>174100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204559</t>
+          <t>204289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27416</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37247</t>
+          <t>35688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54473</t>
+          <t>55601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>60968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>77403</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>50394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67799</t>
+          <t>68166</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116833</t>
+          <t>117378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140392</t>
+          <t>142497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>18713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38726</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35590</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35445</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53695</t>
+          <t>52303</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66041</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91702</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95465</t>
+          <t>95765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118517</t>
+          <t>118473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80291</t>
+          <t>80954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>102130</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>183350</t>
+          <t>182709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>213703</t>
+          <t>214159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47581</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82773</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>111985</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>68816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63978</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95471</t>
+          <t>93858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>126870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96390</t>
+          <t>95845</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>125929</t>
+          <t>126992</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>145018</t>
+          <t>145617</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>181033</t>
+          <t>179194</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>248952</t>
+          <t>249523</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>293530</t>
+          <t>296990</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>336336</t>
+          <t>337753</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>373170</t>
+          <t>374853</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>284688</t>
+          <t>286140</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>323452</t>
+          <t>326805</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>630973</t>
+          <t>631960</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>686263</t>
+          <t>689398</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>57309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>21516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32054</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>32037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32921</t>
+          <t>32629</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>39177</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59743</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42639</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41467</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59520</t>
+          <t>59282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89226</t>
+          <t>90485</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114357</t>
+          <t>113666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36510</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28056</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>55418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>27780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>45473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60691</t>
+          <t>59177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>73523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98631</t>
+          <t>98183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76683</t>
+          <t>76810</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96738</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59275</t>
+          <t>59936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>81412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142956</t>
+          <t>142133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170368</t>
+          <t>170678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>27241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>40872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>36832</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16043</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>29630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37955</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>57459</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55050</t>
+          <t>55441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72160</t>
+          <t>72819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48390</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66611</t>
+          <t>66841</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107973</t>
+          <t>108498</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132855</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>46113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>49572</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63919</t>
+          <t>64827</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90442</t>
+          <t>91855</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72421</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92601</t>
+          <t>93526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67745</t>
+          <t>67766</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88436</t>
+          <t>88655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146043</t>
+          <t>146519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176981</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58626</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83530</t>
+          <t>84310</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92761</t>
+          <t>92273</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126248</t>
+          <t>125713</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>53881</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>78965</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,49 +7231,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>70773</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>58276</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>82640</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>14,85%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>70773</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>58143</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>83679</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>195</t>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118671</t>
+          <t>118866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>156882</t>
+          <t>155085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103521</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134384</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123523</t>
+          <t>123483</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157252</t>
+          <t>157718</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>235970</t>
+          <t>235056</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>281146</t>
+          <t>278992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>266822</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>237934</t>
+          <t>236549</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>275770</t>
+          <t>275456</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>514826</t>
+          <t>514186</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>568757</t>
+          <t>567982</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>37381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36227</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39838</t>
+          <t>39825</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>47627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63886</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57003</t>
+          <t>57468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92211</t>
+          <t>91962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115050</t>
+          <t>115689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,22%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>37182</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>56247</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64494</t>
+          <t>65303</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>89029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99243</t>
+          <t>99558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117925</t>
+          <t>118844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80514</t>
+          <t>80625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102190</t>
+          <t>102164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183450</t>
+          <t>185188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213707</t>
+          <t>213947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23438</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54728</t>
+          <t>54308</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63706</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79805</t>
+          <t>79655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>59107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76934</t>
+          <t>77756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127512</t>
+          <t>126039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152613</t>
+          <t>151703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>32466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23107</t>
+          <t>23454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52663</t>
+          <t>53131</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64143</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89413</t>
+          <t>88924</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>83488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104229</t>
+          <t>104392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>71919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93181</t>
+          <t>92175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161212</t>
+          <t>161013</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189610</t>
+          <t>190396</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>37075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>63514</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67191</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94749</t>
+          <t>95879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>67678</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57885</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83760</t>
+          <t>83776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>107131</t>
+          <t>106281</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142754</t>
+          <t>141009</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>91196</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121706</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>121423</t>
+          <t>124718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157620</t>
+          <t>159599</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>225360</t>
+          <t>223298</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>271412</t>
+          <t>269011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>310857</t>
+          <t>311662</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>347698</t>
+          <t>349488</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>269854</t>
+          <t>270464</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>309996</t>
+          <t>308918</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>590482</t>
+          <t>592724</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>645371</t>
+          <t>646396</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>71861</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>37729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>27099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49242</t>
+          <t>50147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52681</t>
+          <t>53641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67795</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55580</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84961</t>
+          <t>81994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112868</t>
+          <t>113159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144173</t>
+          <t>145232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26857</t>
+          <t>26760</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41761</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37763</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65524</t>
+          <t>63414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66850</t>
+          <t>66203</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97667</t>
+          <t>99542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89911</t>
+          <t>88666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114600</t>
+          <t>114334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99932</t>
+          <t>101023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129122</t>
+          <t>128409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197715</t>
+          <t>199703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235587</t>
+          <t>236042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52665</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>34563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45795</t>
+          <t>45889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>44436</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>49010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>49067</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87708</t>
+          <t>86222</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95540</t>
+          <t>95729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138210</t>
+          <t>134097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77271</t>
+          <t>77500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103435</t>
+          <t>104191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181191</t>
+          <t>180553</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235375</t>
+          <t>234739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27136</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25488</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>33633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>41611</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45371</t>
+          <t>46132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68693</t>
+          <t>69476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81508</t>
+          <t>80359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101770</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72876</t>
+          <t>71221</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94252</t>
+          <t>92996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160043</t>
+          <t>160758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>187592</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47787</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49063</t>
+          <t>49780</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75861</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>92485</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95399</t>
+          <t>94933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>136608</t>
+          <t>135024</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80967</t>
+          <t>81174</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119258</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>122122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>166564</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213713</t>
+          <t>215339</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>272799</t>
+          <t>272458</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>341443</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>397804</t>
+          <t>399413</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>329371</t>
+          <t>330449</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>384852</t>
+          <t>384480</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,47 +14776,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>723984</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>689942</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>768008</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>58,95%</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>723984</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>688594</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>763954</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64588</t>
+          <t>65499</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70638</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>109548</t>
+          <t>107981</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Habitat-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2233,25 +2233,25 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>91000</v>
+        <v>91650</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>79872</v>
+        <v>80708</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>101372</v>
+        <v>102067</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5330653541970052</v>
+        <v>0.5368734235362517</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.467878534772968</v>
+        <v>0.4727774150825765</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5938224999225249</v>
+        <v>0.5978916677105044</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>140</v>
@@ -2275,25 +2275,25 @@
         <v>0.6689341165448572</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>198168</v>
+        <v>198818</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>182468</v>
+        <v>183303</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>212229</v>
+        <v>213292</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5713091192338497</v>
+        <v>0.5731832724330611</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5260485462926356</v>
+        <v>0.5284556474415246</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.6118469164260955</v>
+        <v>0.6149127207195701</v>
       </c>
     </row>
     <row r="26">
@@ -2304,25 +2304,25 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>9528</v>
+        <v>8878</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5346</v>
+        <v>4789</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>14298</v>
+        <v>13474</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05581356358318115</v>
+        <v>0.05200549424393466</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.03131523978294744</v>
+        <v>0.02805602788864052</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.08375533275067366</v>
+        <v>0.07892610568760462</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>9</v>
@@ -2346,25 +2346,25 @@
         <v>0.06788517193933953</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>16170</v>
+        <v>15520</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>10581</v>
+        <v>9947</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>23162</v>
+        <v>22451</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.04661774374117035</v>
+        <v>0.044743590541959</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.03050347955643616</v>
+        <v>0.02867773930632453</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.06677517010387231</v>
+        <v>0.06472596801525331</v>
       </c>
     </row>
     <row r="27">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2663,25 +2663,25 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>304213</v>
+        <v>304863</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>285570</v>
+        <v>286131</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>324293</v>
+        <v>324710</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.5024551392778183</v>
+        <v>0.5035288487457855</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4716626792796453</v>
+        <v>0.4725897824735413</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5356197657406884</v>
+        <v>0.5363088091232465</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>525</v>
@@ -2705,25 +2705,25 @@
         <v>0.6454744660949693</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>659528</v>
+        <v>660178</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>633140</v>
+        <v>633820</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>687943</v>
+        <v>688456</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5572576635126306</v>
+        <v>0.5578069385938749</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.5349609214065915</v>
+        <v>0.5355359463257564</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5812662489721956</v>
+        <v>0.5816993726167565</v>
       </c>
     </row>
     <row r="32">
@@ -2734,25 +2734,25 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>26250</v>
+        <v>25599</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>19267</v>
+        <v>18573</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>34699</v>
+        <v>34180</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.04335525635786645</v>
+        <v>0.04228154688989916</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.03182265127449958</v>
+        <v>0.03067645825931641</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.05731068622694988</v>
+        <v>0.0564528716715501</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>29</v>
@@ -2776,25 +2776,25 @@
         <v>0.0458607535520415</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R32" s="5" t="n">
-        <v>45282</v>
+        <v>44632</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>36104</v>
+        <v>35378</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>57176</v>
+        <v>56272</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.03826000231423884</v>
+        <v>0.03771072723299453</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.03050524197936881</v>
+        <v>0.02989174778838683</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.04830994509272634</v>
+        <v>0.04754635947722598</v>
       </c>
     </row>
     <row r="33">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
